--- a/sheets/대금율보/검수/대금산조 잦은모리.xlsx
+++ b/sheets/대금율보/검수/대금산조 잦은모리.xlsx
@@ -19385,7 +19385,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I5" s="24"/>
@@ -19440,7 +19440,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 –
 △</t>
         </is>
@@ -19525,7 +19525,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?
+          <t xml:space="preserve">潢
 汰
 –</t>
         </is>
@@ -19600,7 +19600,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 㳞
 –</t>
         </is>
@@ -19661,7 +19661,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C9" s="24"/>
@@ -19758,13 +19758,13 @@
       <c r="I10" s="22"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K10" s="24"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 –
 △</t>
         </is>
@@ -19772,7 +19772,7 @@
       <c r="M10" s="24"/>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 –
 △</t>
         </is>
@@ -19788,7 +19788,7 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 –
 △</t>
         </is>
@@ -19796,7 +19796,7 @@
       <c r="S10" s="24"/>
       <c r="T10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 –
 △</t>
         </is>
@@ -19920,7 +19920,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -20051,7 +20051,7 @@
       <c r="S15" s="22"/>
       <c r="T15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="U15" s="24"/>
@@ -20884,7 +20884,7 @@
       <c r="H29" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?
+仲
 太</t>
         </is>
       </c>
@@ -20952,7 +20952,7 @@
       <c r="G30" s="22"/>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 太
 △</t>
         </is>
@@ -21039,7 +21039,7 @@
       <c r="C33" s="22"/>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 –
 㳞</t>
         </is>
@@ -21073,7 +21073,7 @@
         <is>
           <t xml:space="preserve">汰
 –
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="M33" s="24"/>
@@ -21747,7 +21747,7 @@
       <c r="P44" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-淋?
+淋
 –</t>
         </is>
       </c>
@@ -21787,7 +21787,7 @@
       <c r="E45" s="22"/>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">南?</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G45" s="24"/>
@@ -22033,7 +22033,7 @@
       <c r="N48" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-淋?
+淋
 –</t>
         </is>
       </c>
@@ -22041,7 +22041,7 @@
       <c r="P48" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潕?
+潕
 –</t>
         </is>
       </c>
@@ -22411,7 +22411,7 @@
       <c r="I55" s="22"/>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K55" s="24"/>
@@ -22536,7 +22536,7 @@
       <c r="F57" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?
+仲
 太</t>
         </is>
       </c>
@@ -22569,7 +22569,7 @@
       <c r="O57" s="22"/>
       <c r="P57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="Q57" s="24"/>
@@ -22630,7 +22630,7 @@
       <c r="S58" s="22"/>
       <c r="T58" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 林
 太</t>
         </is>
@@ -22654,7 +22654,7 @@
       <c r="H59" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?
+仲
 太</t>
         </is>
       </c>
@@ -22692,7 +22692,7 @@
       <c r="A60" s="0"/>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C60" s="24"/>
@@ -22808,7 +22808,7 @@
       <c r="F63" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?
+仲
 太</t>
         </is>
       </c>
@@ -22833,7 +22833,7 @@
         <is>
           <t xml:space="preserve">汰
 –
-南?</t>
+南</t>
         </is>
       </c>
       <c r="O63" s="24"/>
@@ -22847,7 +22847,7 @@
         <is>
           <t xml:space="preserve">淋
 潕
-淋?</t>
+淋</t>
         </is>
       </c>
       <c r="S63" s="24"/>
@@ -22864,7 +22864,7 @@
       <c r="A64" s="0"/>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C64" s="24"/>
@@ -22889,7 +22889,7 @@
       <c r="N64" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-淋?
+淋
 –</t>
         </is>
       </c>
@@ -22961,7 +22961,7 @@
       <c r="S65" s="22"/>
       <c r="T65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?
+          <t xml:space="preserve">㳞
 –
 淋</t>
         </is>
@@ -23004,7 +23004,7 @@
       <c r="O66" s="22"/>
       <c r="P66" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 –
 △</t>
         </is>
@@ -23031,7 +23031,7 @@
       <c r="A67" s="0"/>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C67" s="24"/>
@@ -23044,7 +23044,7 @@
       <c r="F67" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?
+仲
 太</t>
         </is>
       </c>
@@ -23069,7 +23069,7 @@
       <c r="M67" s="22"/>
       <c r="N67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕?
+          <t xml:space="preserve">潕
 –
 淋</t>
         </is>
@@ -23077,7 +23077,7 @@
       <c r="O67" s="24"/>
       <c r="P67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 –
 淋</t>
         </is>
@@ -23087,7 +23087,7 @@
         <is>
           <t xml:space="preserve">汰
 –
-南?</t>
+南</t>
         </is>
       </c>
       <c r="S67" s="24"/>
@@ -23095,7 +23095,7 @@
         <is>
           <t xml:space="preserve">汰
 –
-南?</t>
+南</t>
         </is>
       </c>
       <c r="U67" s="24"/>
@@ -23309,7 +23309,7 @@
       <c r="A73" s="0"/>
       <c r="B73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C73" s="24"/>
@@ -23346,7 +23346,7 @@
       <c r="N73" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潕ㄷ
-淋?
+淋
 淋</t>
         </is>
       </c>
@@ -23354,7 +23354,7 @@
       <c r="P73" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-淋?
+淋
 㳞</t>
         </is>
       </c>
@@ -23407,7 +23407,7 @@
       <c r="N74" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潕ㄷ
-淋?
+淋
 淋</t>
         </is>
       </c>
@@ -23478,7 +23478,7 @@
       <c r="P75" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-淋?
+淋
 㳞</t>
         </is>
       </c>
@@ -23488,7 +23488,7 @@
       <c r="T75" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-淋?
+淋
 㳞</t>
         </is>
       </c>
@@ -23581,7 +23581,7 @@
       <c r="G77" s="22"/>
       <c r="H77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I77" s="24"/>
@@ -23608,7 +23608,7 @@
       <c r="P77" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-淋?
+淋
 㳞</t>
         </is>
       </c>
@@ -23704,7 +23704,7 @@
       <c r="P79" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-淋?
+淋
 㳞</t>
         </is>
       </c>
@@ -23714,7 +23714,7 @@
       <c r="T79" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-淋?
+淋
 㳞</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/대금산조 잦은모리.xlsx
+++ b/sheets/대금율보/검수/대금산조 잦은모리.xlsx
@@ -19163,32 +19163,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="178.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="178.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="178.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="178.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="178.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="178.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="178.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="178.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -19803,10 +19803,10 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11">
+    <row r="11" ht="6.0" customHeight="true">
       <c r="A11" s="0"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="80.0" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="178.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="178.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="178.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -20056,7 +20056,7 @@
       </c>
       <c r="U15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="178.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="178.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="178.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="178.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="178.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -20419,10 +20419,10 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21">
+    <row r="21" ht="6.0" customHeight="true">
       <c r="A21" s="0"/>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="80.0" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="20" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="178.84" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="178.84" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="22"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="178.84" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="178.84" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="U26" s="26"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="178.84" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
       </c>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="178.84" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="22"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="178.84" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
       <c r="T29" s="21"/>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="178.84" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21" t="inlineStr">
         <is>
@@ -20999,10 +20999,10 @@
       </c>
       <c r="U30" s="22"/>
     </row>
-    <row r="31">
+    <row r="31" ht="6.0" customHeight="true">
       <c r="A31" s="0"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="80.0" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="20" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
       <c r="T32" s="20"/>
       <c r="U32" s="20"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="178.84" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="178.84" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="178.84" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="22"/>
@@ -21238,7 +21238,7 @@
       </c>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="178.84" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="22"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="U36" s="22"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="178.84" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="178.84" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="22"/>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="U38" s="22"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="178.84" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="22"/>
@@ -21500,7 +21500,7 @@
       </c>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="178.84" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -21581,10 +21581,10 @@
       </c>
       <c r="U40" s="22"/>
     </row>
-    <row r="41">
+    <row r="41" ht="6.0" customHeight="true">
       <c r="A41" s="0"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="80.0" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="20" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
       <c r="T42" s="20"/>
       <c r="U42" s="20"/>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="178.84" customHeight="true">
       <c r="A43" s="0"/>
       <c r="B43" s="21" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
       </c>
       <c r="U43" s="22"/>
     </row>
-    <row r="44" ht="56" customHeight="1">
+    <row r="44" ht="178.84" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="21" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
       </c>
       <c r="U44" s="22"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="178.84" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="178.84" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
       </c>
       <c r="U46" s="22"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="178.84" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="U47" s="22"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="178.84" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="U48" s="22"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="178.84" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="U49" s="22"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="178.84" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -22205,10 +22205,10 @@
       </c>
       <c r="U50" s="22"/>
     </row>
-    <row r="51">
+    <row r="51" ht="6.0" customHeight="true">
       <c r="A51" s="0"/>
     </row>
-    <row r="52" ht="60" customHeight="1">
+    <row r="52" ht="80.0" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="20" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
       <c r="T52" s="20"/>
       <c r="U52" s="20"/>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="178.84" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="U53" s="22"/>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="178.84" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
       </c>
       <c r="U54" s="22"/>
     </row>
-    <row r="55" ht="56" customHeight="1">
+    <row r="55" ht="178.84" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
       </c>
       <c r="U55" s="22"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="178.84" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="U56" s="22"/>
     </row>
-    <row r="57" ht="56" customHeight="1">
+    <row r="57" ht="178.84" customHeight="true">
       <c r="A57" s="0"/>
       <c r="B57" s="21" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="U57" s="22"/>
     </row>
-    <row r="58" ht="56" customHeight="1">
+    <row r="58" ht="178.84" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="21" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="U58" s="24"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="178.84" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
       </c>
       <c r="U59" s="22"/>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="178.84" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="23" t="inlineStr">
         <is>
@@ -22765,10 +22765,10 @@
       </c>
       <c r="U60" s="22"/>
     </row>
-    <row r="61">
+    <row r="61" ht="6.0" customHeight="true">
       <c r="A61" s="0"/>
     </row>
-    <row r="62" ht="60" customHeight="1">
+    <row r="62" ht="80.0" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="20" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
       <c r="T62" s="20"/>
       <c r="U62" s="20"/>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="178.84" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
       </c>
       <c r="U63" s="22"/>
     </row>
-    <row r="64" ht="56" customHeight="1">
+    <row r="64" ht="178.84" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="23" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
       </c>
       <c r="U64" s="22"/>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="178.84" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21"/>
       <c r="C65" s="22"/>
@@ -22968,7 +22968,7 @@
       </c>
       <c r="U65" s="24"/>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="178.84" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21"/>
       <c r="C66" s="22"/>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="U66" s="22"/>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="178.84" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="23" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="U67" s="24"/>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="178.84" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
       </c>
       <c r="U68" s="22"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="178.84" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21"/>
       <c r="C69" s="22"/>
@@ -23218,7 +23218,7 @@
       </c>
       <c r="U69" s="22"/>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="178.84" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21"/>
       <c r="C70" s="22"/>
@@ -23275,10 +23275,10 @@
       </c>
       <c r="U70" s="22"/>
     </row>
-    <row r="71">
+    <row r="71" ht="6.0" customHeight="true">
       <c r="A71" s="0"/>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72" ht="80.0" customHeight="true">
       <c r="A72" s="0"/>
       <c r="B72" s="20" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
       <c r="T72" s="20"/>
       <c r="U72" s="20"/>
     </row>
-    <row r="73" ht="56" customHeight="1">
+    <row r="73" ht="178.84" customHeight="true">
       <c r="A73" s="0"/>
       <c r="B73" s="23" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
       </c>
       <c r="U73" s="22"/>
     </row>
-    <row r="74" ht="56" customHeight="1">
+    <row r="74" ht="178.84" customHeight="true">
       <c r="A74" s="0"/>
       <c r="B74" s="21" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
       </c>
       <c r="U74" s="22"/>
     </row>
-    <row r="75" ht="56" customHeight="1">
+    <row r="75" ht="178.84" customHeight="true">
       <c r="A75" s="0"/>
       <c r="B75" s="21"/>
       <c r="C75" s="22"/>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="U75" s="24"/>
     </row>
-    <row r="76" ht="56" customHeight="1">
+    <row r="76" ht="178.84" customHeight="true">
       <c r="A76" s="0"/>
       <c r="B76" s="21" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="U76" s="22"/>
     </row>
-    <row r="77" ht="56" customHeight="1">
+    <row r="77" ht="178.84" customHeight="true">
       <c r="A77" s="0"/>
       <c r="B77" s="21" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
       </c>
       <c r="U77" s="22"/>
     </row>
-    <row r="78" ht="56" customHeight="1">
+    <row r="78" ht="178.84" customHeight="true">
       <c r="A78" s="0"/>
       <c r="B78" s="21" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="U78" s="22"/>
     </row>
-    <row r="79" ht="56" customHeight="1">
+    <row r="79" ht="178.84" customHeight="true">
       <c r="A79" s="0"/>
       <c r="B79" s="21" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
       </c>
       <c r="U79" s="24"/>
     </row>
-    <row r="80" ht="56" customHeight="1">
+    <row r="80" ht="178.84" customHeight="true">
       <c r="A80" s="0"/>
       <c r="B80" s="21" t="inlineStr">
         <is>
@@ -23771,10 +23771,10 @@
       </c>
       <c r="U80" s="22"/>
     </row>
-    <row r="81">
+    <row r="81" ht="6.0" customHeight="true">
       <c r="A81" s="0"/>
     </row>
-    <row r="82" ht="60" customHeight="1">
+    <row r="82" ht="80.0" customHeight="true">
       <c r="A82" s="0"/>
       <c r="B82" s="20" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
       <c r="T82" s="20"/>
       <c r="U82" s="20"/>
     </row>
-    <row r="83" ht="56" customHeight="1">
+    <row r="83" ht="178.84" customHeight="true">
       <c r="A83" s="0"/>
       <c r="B83" s="21"/>
       <c r="C83" s="22"/>
@@ -23824,7 +23824,7 @@
       <c r="T83" s="21"/>
       <c r="U83" s="22"/>
     </row>
-    <row r="84" ht="56" customHeight="1">
+    <row r="84" ht="178.84" customHeight="true">
       <c r="A84" s="0"/>
       <c r="B84" s="21"/>
       <c r="C84" s="22"/>
@@ -23847,7 +23847,7 @@
       <c r="T84" s="21"/>
       <c r="U84" s="22"/>
     </row>
-    <row r="85" ht="56" customHeight="1">
+    <row r="85" ht="178.84" customHeight="true">
       <c r="A85" s="0"/>
       <c r="B85" s="21"/>
       <c r="C85" s="22"/>
@@ -23874,7 +23874,7 @@
       </c>
       <c r="U85" s="22"/>
     </row>
-    <row r="86" ht="56" customHeight="1">
+    <row r="86" ht="178.84" customHeight="true">
       <c r="A86" s="0"/>
       <c r="B86" s="21"/>
       <c r="C86" s="22"/>
@@ -23901,7 +23901,7 @@
       <c r="T86" s="21"/>
       <c r="U86" s="22"/>
     </row>
-    <row r="87" ht="56" customHeight="1">
+    <row r="87" ht="178.84" customHeight="true">
       <c r="A87" s="0"/>
       <c r="B87" s="21"/>
       <c r="C87" s="22"/>
@@ -23930,7 +23930,7 @@
       </c>
       <c r="U87" s="22"/>
     </row>
-    <row r="88" ht="56" customHeight="1">
+    <row r="88" ht="178.84" customHeight="true">
       <c r="A88" s="0"/>
       <c r="B88" s="21"/>
       <c r="C88" s="22"/>
@@ -23953,7 +23953,7 @@
       <c r="T88" s="21"/>
       <c r="U88" s="22"/>
     </row>
-    <row r="89" ht="56" customHeight="1">
+    <row r="89" ht="178.84" customHeight="true">
       <c r="A89" s="0"/>
       <c r="B89" s="21"/>
       <c r="C89" s="22"/>
@@ -23980,7 +23980,7 @@
       </c>
       <c r="U89" s="22"/>
     </row>
-    <row r="90" ht="56" customHeight="1">
+    <row r="90" ht="178.84" customHeight="true">
       <c r="A90" s="0"/>
       <c r="B90" s="21"/>
       <c r="C90" s="22"/>
@@ -24017,7 +24017,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="8" manualBreakCount="8">
     <brk id="10" max="16383" man="1"/>
     <brk id="20" max="16383" man="1"/>
